--- a/annexes/E5 -Tableau de synthese.xlsx
+++ b/annexes/E5 -Tableau de synthese.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BTS\Portfolio_BTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BTS\Portfolio_BTS\annexes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDBD08B-BCA0-490C-B50C-C8F67F93A4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BF7F53-8FE7-4626-ACA4-4ABC52C1B1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="101716"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -156,6 +156,18 @@
   </si>
   <si>
     <t>10/09/2024 au 08/10/2024</t>
+  </si>
+  <si>
+    <t>WorkTogether</t>
+  </si>
+  <si>
+    <t>SpaceHub</t>
+  </si>
+  <si>
+    <t>14/11/2025 au 28/11/2025</t>
+  </si>
+  <si>
+    <t>28/11/2025 au 12/04/2026</t>
   </si>
 </sst>
 </file>
@@ -165,7 +177,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -227,6 +239,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -633,7 +651,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -707,13 +725,37 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -749,29 +791,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1081,7 +1111,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ65"/>
+  <dimension ref="A1:AQ67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="9" customWidth="1"/>
@@ -1092,56 +1122,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="46"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="10" t="s">
         <v>8</v>
       </c>
@@ -1153,22 +1183,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="42" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1191,18 +1221,18 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="13" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="49" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
@@ -1248,16 +1278,16 @@
       <c r="AQ7" s="8"/>
     </row>
     <row r="8" spans="1:43" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
@@ -1304,7 +1334,7 @@
       <c r="C9" s="15"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="F9" s="50"/>
       <c r="G9" s="16"/>
       <c r="H9" s="23" t="s">
         <v>27</v>
@@ -1357,9 +1387,7 @@
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="F10" s="47"/>
       <c r="G10" s="16"/>
       <c r="H10" s="23" t="s">
         <v>27</v>
@@ -1401,14 +1429,18 @@
       <c r="AQ10" s="8"/>
     </row>
     <row r="11" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="48"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -1445,17 +1477,19 @@
       <c r="AP11" s="8"/>
       <c r="AQ11" s="8"/>
     </row>
-    <row r="12" spans="1:43" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
+    <row r="12" spans="1:43" s="13" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1492,20 +1526,12 @@
       <c r="AP12" s="8"/>
       <c r="AQ12" s="8"/>
     </row>
-    <row r="13" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>27</v>
-      </c>
+    <row r="13" spans="1:43" s="13" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="16"/>
       <c r="D13" s="16"/>
-      <c r="E13" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
@@ -1545,25 +1571,17 @@
       <c r="AP13" s="8"/>
       <c r="AQ13" s="8"/>
     </row>
-    <row r="14" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="17"/>
+    <row r="14" spans="1:43" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A14" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -1601,11 +1619,17 @@
       <c r="AQ14" s="8"/>
     </row>
     <row r="15" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="16"/>
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="47"/>
       <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="E15" s="24" t="s">
+        <v>27</v>
+      </c>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
       <c r="H15" s="17"/>
@@ -1645,17 +1669,25 @@
       <c r="AP15" s="8"/>
       <c r="AQ15" s="8"/>
     </row>
-    <row r="16" spans="1:43" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="33"/>
+    <row r="16" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="17"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
@@ -1692,26 +1724,14 @@
       <c r="AP16" s="8"/>
       <c r="AQ16" s="8"/>
     </row>
-    <row r="17" spans="1:43" s="13" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>27</v>
-      </c>
+    <row r="17" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
       <c r="H17" s="17"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -1749,15 +1769,17 @@
       <c r="AP17" s="8"/>
       <c r="AQ17" s="8"/>
     </row>
-    <row r="18" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="21"/>
+    <row r="18" spans="1:43" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
@@ -1794,15 +1816,25 @@
       <c r="AP18" s="8"/>
       <c r="AQ18" s="8"/>
     </row>
-    <row r="19" spans="1:43" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+    <row r="19" spans="1:43" s="13" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="17"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -1839,8 +1871,96 @@
       <c r="AP19" s="8"/>
       <c r="AQ19" s="8"/>
     </row>
-    <row r="20" spans="1:43" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:43" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:43" s="13" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8"/>
+      <c r="AD20" s="8"/>
+      <c r="AE20" s="8"/>
+      <c r="AF20" s="8"/>
+      <c r="AG20" s="8"/>
+      <c r="AH20" s="8"/>
+      <c r="AI20" s="8"/>
+      <c r="AJ20" s="8"/>
+      <c r="AK20" s="8"/>
+      <c r="AL20" s="8"/>
+      <c r="AM20" s="8"/>
+      <c r="AN20" s="8"/>
+      <c r="AO20" s="8"/>
+      <c r="AP20" s="8"/>
+      <c r="AQ20" s="8"/>
+    </row>
+    <row r="21" spans="1:43" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
+      <c r="AE21" s="8"/>
+      <c r="AF21" s="8"/>
+      <c r="AG21" s="8"/>
+      <c r="AH21" s="8"/>
+      <c r="AI21" s="8"/>
+      <c r="AJ21" s="8"/>
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="8"/>
+      <c r="AN21" s="8"/>
+      <c r="AO21" s="8"/>
+      <c r="AP21" s="8"/>
+      <c r="AQ21" s="8"/>
+    </row>
     <row r="22" spans="1:43" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:43" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:43" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1885,25 +2005,27 @@
     <row r="63" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="64" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="65" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/annexes/E5 -Tableau de synthese.xlsx
+++ b/annexes/E5 -Tableau de synthese.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Tableau de synthèse Épreuve E5'!$A$1:$H$21</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Tableau de synthèse Épreuve E5'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -135,12 +135,6 @@
   </si>
   <si>
     <t xml:space="preserve">28/11/2025 au 12/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpaceHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/11/2025 au 28/11/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Réalisations en milieu professionnel en cours de première année</t>
@@ -596,139 +590,139 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -985,8 +979,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AQ67"/>
-  <sheetFormatPr defaultColWidth="10.859375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AQ1048576"/>
+  <sheetFormatPr defaultColWidth="10.84765625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="70.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.43"/>
@@ -1346,16 +1340,12 @@
       <c r="AQ11" s="2"/>
     </row>
     <row r="12" s="17" customFormat="true" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>32</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="25"/>
+      <c r="D12" s="22"/>
       <c r="E12" s="22"/>
-      <c r="F12" s="25"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="22"/>
       <c r="H12" s="26"/>
       <c r="I12" s="2"/>
@@ -1394,15 +1384,17 @@
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2"/>
     </row>
-    <row r="13" s="17" customFormat="true" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="26"/>
+    <row r="13" s="17" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1439,17 +1431,19 @@
       <c r="AP13" s="2"/>
       <c r="AQ13" s="2"/>
     </row>
-    <row r="14" s="17" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="s">
+    <row r="14" s="17" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="26"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1493,11 +1487,11 @@
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="26"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -1536,17 +1530,13 @@
       <c r="AQ15" s="2"/>
     </row>
     <row r="16" s="17" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
-      <c r="G16" s="25"/>
+      <c r="G16" s="22"/>
       <c r="H16" s="26"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1584,15 +1574,17 @@
       <c r="AP16" s="2"/>
       <c r="AQ16" s="2"/>
     </row>
-    <row r="17" s="17" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="26"/>
+    <row r="17" s="17" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1629,17 +1621,19 @@
       <c r="AP17" s="2"/>
       <c r="AQ17" s="2"/>
     </row>
-    <row r="18" s="17" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+    <row r="18" s="17" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1676,19 +1670,15 @@
       <c r="AP18" s="2"/>
       <c r="AQ18" s="2"/>
     </row>
-    <row r="19" s="17" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26"/>
+    <row r="19" s="17" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1725,15 +1715,15 @@
       <c r="AP19" s="2"/>
       <c r="AQ19" s="2"/>
     </row>
-    <row r="20" s="17" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
+    <row r="20" s="17" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1770,51 +1760,7 @@
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
     </row>
-    <row r="21" s="17" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
-      <c r="AG21" s="2"/>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-      <c r="AQ21" s="2"/>
-    </row>
+    <row r="21" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="22" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="24" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1860,7 +1806,7 @@
     <row r="64" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="65" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="66" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A1:F1"/>
@@ -1873,8 +1819,8 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
